--- a/data/trans_orig/P16A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50720</t>
+          <t>51906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103942</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222290</t>
+          <t>221104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245851</t>
+          <t>245163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198235</t>
+          <t>198967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224511</t>
+          <t>224278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429906</t>
+          <t>431316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>463680</t>
+          <t>463730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61241</t>
+          <t>60598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94783</t>
+          <t>95327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130194</t>
+          <t>130379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137495</t>
+          <t>137789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183565</t>
+          <t>182319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431834</t>
+          <t>432477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458518</t>
+          <t>458869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373755</t>
+          <t>373570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409166</t>
+          <t>408622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813459</t>
+          <t>814705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859529</t>
+          <t>859235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81609</t>
+          <t>80564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>113369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112093</t>
+          <t>112602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153313</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272002</t>
+          <t>270034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294927</t>
+          <t>293562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>222043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253803</t>
+          <t>254848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500945</t>
+          <t>501229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542165</t>
+          <t>541656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>68219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>68142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99774</t>
+          <t>100881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117163</t>
+          <t>116694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158692</t>
+          <t>159498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291715</t>
+          <t>290452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317988</t>
+          <t>316156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271682</t>
+          <t>270575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302730</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571435</t>
+          <t>570629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>612964</t>
+          <t>613433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39552</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66110</t>
+          <t>65446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>98752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163647</t>
+          <t>163267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182980</t>
+          <t>183110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141499</t>
+          <t>142229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>167376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312944</t>
+          <t>312224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344866</t>
+          <t>345530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>26543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54729</t>
+          <t>55733</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83917</t>
+          <t>82758</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88768</t>
+          <t>87080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123121</t>
+          <t>123815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222990</t>
+          <t>222664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243852</t>
+          <t>244268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194227</t>
+          <t>195386</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223415</t>
+          <t>222411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425834</t>
+          <t>425140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>460187</t>
+          <t>461875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72200</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106342</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112687</t>
+          <t>112440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152146</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194416</t>
+          <t>194216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248974</t>
+          <t>248456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>508685</t>
+          <t>511256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>545930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>486073</t>
+          <t>481794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>525532</t>
+          <t>525779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1004272</t>
+          <t>1004790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1058830</t>
+          <t>1059030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111704</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154305</t>
+          <t>151505</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184831</t>
+          <t>188930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238065</t>
+          <t>238819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>314526</t>
+          <t>312675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>378642</t>
+          <t>378531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>588472</t>
+          <t>591272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>631073</t>
+          <t>632612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>544692</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>598680</t>
+          <t>594581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147646</t>
+          <t>1147757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1211762</t>
+          <t>1213613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>419332</t>
+          <t>419788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>499643</t>
+          <t>494030</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>760960</t>
+          <t>758119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>859025</t>
+          <t>857376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1199751</t>
+          <t>1197256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1327515</t>
+          <t>1327501</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2775882</t>
+          <t>2781495</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2856193</t>
+          <t>2855737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2520172</t>
+          <t>2521821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2618237</t>
+          <t>2621078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5327207</t>
+          <t>5327221</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5454971</t>
+          <t>5457466</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>36868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>63731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89471</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102467</t>
+          <t>103136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144586</t>
+          <t>145189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227483</t>
+          <t>228464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255123</t>
+          <t>255327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194511</t>
+          <t>194428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224324</t>
+          <t>225018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431590</t>
+          <t>430987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473709</t>
+          <t>473040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>89183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126785</t>
+          <t>126068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159743</t>
+          <t>160619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204529</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257622</t>
+          <t>257106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317945</t>
+          <t>317915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378742</t>
+          <t>379459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415682</t>
+          <t>416344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318202</t>
+          <t>318918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362988</t>
+          <t>362112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710313</t>
+          <t>710343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770636</t>
+          <t>771152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>58135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>88334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92030</t>
+          <t>92127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127728</t>
+          <t>128570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158458</t>
+          <t>157886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205440</t>
+          <t>206079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>235896</t>
+          <t>234782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265792</t>
+          <t>264981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213292</t>
+          <t>212450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248990</t>
+          <t>248893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458696</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505678</t>
+          <t>506250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91519</t>
+          <t>91562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140485</t>
+          <t>138668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180370</t>
+          <t>176540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>207075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256438</t>
+          <t>258288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282463</t>
+          <t>282420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315814</t>
+          <t>316389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207604</t>
+          <t>211434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247489</t>
+          <t>249306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>505518</t>
+          <t>503668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557411</t>
+          <t>554881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48039</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82415</t>
+          <t>83260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111495</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115499</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156099</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164579</t>
+          <t>164611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187529</t>
+          <t>186801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108096</t>
+          <t>105858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137176</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276110</t>
+          <t>277026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316710</t>
+          <t>318126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41299</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67119</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>88937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120500</t>
+          <t>122950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>139312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181575</t>
+          <t>180351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206862</t>
+          <t>207434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232682</t>
+          <t>233243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158640</t>
+          <t>156190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189131</t>
+          <t>190203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371546</t>
+          <t>372770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413948</t>
+          <t>413809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90997</t>
+          <t>93126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132446</t>
+          <t>137042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199877</t>
+          <t>199740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248255</t>
+          <t>249451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302736</t>
+          <t>304721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>366369</t>
+          <t>371436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>530342</t>
+          <t>525746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571791</t>
+          <t>569662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>445598</t>
+          <t>444402</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>493976</t>
+          <t>494113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>990272</t>
+          <t>985205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1053905</t>
+          <t>1051920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92515</t>
+          <t>91910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133011</t>
+          <t>132566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212604</t>
+          <t>213168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267211</t>
+          <t>266891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>314144</t>
+          <t>317768</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>384069</t>
+          <t>386917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>643961</t>
+          <t>644406</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>684457</t>
+          <t>685062</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>555492</t>
+          <t>555812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>610099</t>
+          <t>609535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1215606</t>
+          <t>1212758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1285531</t>
+          <t>1281907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>566113</t>
+          <t>564915</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>663418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1129279</t>
+          <t>1134909</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1248204</t>
+          <t>1247662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1728497</t>
+          <t>1729485</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1880953</t>
+          <t>1884212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2762790</t>
+          <t>2757761</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2855066</t>
+          <t>2856264</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2302791</t>
+          <t>2303333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2421716</t>
+          <t>2416086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5091221</t>
+          <t>5087962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5243677</t>
+          <t>5242689</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79621</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81125</t>
+          <t>81202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114866</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138277</t>
+          <t>136679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182946</t>
+          <t>182161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214140</t>
+          <t>215674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244228</t>
+          <t>244651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173837</t>
+          <t>174190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207578</t>
+          <t>207501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399518</t>
+          <t>400303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444187</t>
+          <t>445785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69565</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103304</t>
+          <t>104076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136749</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179668</t>
+          <t>178078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215570</t>
+          <t>215081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271109</t>
+          <t>270119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399271</t>
+          <t>398499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433010</t>
+          <t>431552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343416</t>
+          <t>345006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>386335</t>
+          <t>386900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>754550</t>
+          <t>755540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810089</t>
+          <t>810578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49791</t>
+          <t>50585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77389</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94659</t>
+          <t>93686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>129519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151847</t>
+          <t>152535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196607</t>
+          <t>195234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241176</t>
+          <t>242540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268774</t>
+          <t>267980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208219</t>
+          <t>206790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241650</t>
+          <t>242623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458267</t>
+          <t>459640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>503027</t>
+          <t>502339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88599</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123702</t>
+          <t>123449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158702</t>
+          <t>157214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>198478</t>
+          <t>196745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255554</t>
+          <t>255559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308406</t>
+          <t>308568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246262</t>
+          <t>246515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>281365</t>
+          <t>281412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188805</t>
+          <t>190538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228581</t>
+          <t>230069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448841</t>
+          <t>448679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>501693</t>
+          <t>501688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77839</t>
+          <t>78563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79142</t>
+          <t>79701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111398</t>
+          <t>113522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171551</t>
+          <t>169598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191336</t>
+          <t>190819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140748</t>
+          <t>140024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166824</t>
+          <t>165725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318410</t>
+          <t>316286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350666</t>
+          <t>350107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52791</t>
+          <t>51606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84661</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>90240</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128458</t>
+          <t>130585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210332</t>
+          <t>211517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234631</t>
+          <t>235144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188454</t>
+          <t>188100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217891</t>
+          <t>218483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407780</t>
+          <t>405653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445611</t>
+          <t>445998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80125</t>
+          <t>81334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119526</t>
+          <t>116342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130208</t>
+          <t>132114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174829</t>
+          <t>176017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221112</t>
+          <t>222684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>278831</t>
+          <t>283508</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>537032</t>
+          <t>540216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>576433</t>
+          <t>575224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>516465</t>
+          <t>515277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561086</t>
+          <t>559180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1069021</t>
+          <t>1064344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1126740</t>
+          <t>1125168</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133234</t>
+          <t>135273</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178042</t>
+          <t>181448</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>247524</t>
+          <t>249031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301940</t>
+          <t>302704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>392860</t>
+          <t>394379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>470252</t>
+          <t>467581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600541</t>
+          <t>597135</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>645349</t>
+          <t>643310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>524227</t>
+          <t>523463</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>578643</t>
+          <t>577136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1134498</t>
+          <t>1137169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1211890</t>
+          <t>1210371</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>599790</t>
+          <t>596489</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>685922</t>
+          <t>685443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1043727</t>
+          <t>1045830</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1156043</t>
+          <t>1162104</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1666980</t>
+          <t>1673737</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1821371</t>
+          <t>1828832</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2708428</t>
+          <t>2708907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2794560</t>
+          <t>2797861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2388499</t>
+          <t>2382438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2500815</t>
+          <t>2498712</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5117521</t>
+          <t>5110060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5271912</t>
+          <t>5265155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72757</t>
+          <t>73330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111689</t>
+          <t>111069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112647</t>
+          <t>113308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>141176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193715</t>
+          <t>196644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241604</t>
+          <t>242434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199754</t>
+          <t>200374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238686</t>
+          <t>238113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148263</t>
+          <t>148459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176988</t>
+          <t>176327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>359473</t>
+          <t>358643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407362</t>
+          <t>404433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98673</t>
+          <t>99499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>143140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189453</t>
+          <t>190479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>230515</t>
+          <t>229325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299479</t>
+          <t>299982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>361560</t>
+          <t>360735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375610</t>
+          <t>375250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419717</t>
+          <t>418891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283776</t>
+          <t>284966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324838</t>
+          <t>323812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671120</t>
+          <t>671945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733201</t>
+          <t>732698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76154</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106793</t>
+          <t>108279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131504</t>
+          <t>131834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163371</t>
+          <t>162489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216871</t>
+          <t>215252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259852</t>
+          <t>261360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209257</t>
+          <t>207771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239896</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185757</t>
+          <t>186639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217624</t>
+          <t>217294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>405326</t>
+          <t>403818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>448307</t>
+          <t>449926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76340</t>
+          <t>77197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116789</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97535</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210352</t>
+          <t>211222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194780</t>
+          <t>187397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305072</t>
+          <t>303586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195768</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236217</t>
+          <t>235360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265366</t>
+          <t>264496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378183</t>
+          <t>378844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>483202</t>
+          <t>484688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593494</t>
+          <t>600877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72153</t>
+          <t>72923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91600</t>
+          <t>91156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111599</t>
+          <t>110468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138426</t>
+          <t>136381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127543</t>
+          <t>128353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145675</t>
+          <t>146295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117056</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136503</t>
+          <t>135733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248972</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275799</t>
+          <t>276930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67256</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92751</t>
+          <t>92916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98382</t>
+          <t>98110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>124023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170493</t>
+          <t>171117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207181</t>
+          <t>208596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176885</t>
+          <t>176720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202380</t>
+          <t>203200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133435</t>
+          <t>133033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158674</t>
+          <t>158946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319511</t>
+          <t>318096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356199</t>
+          <t>355575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141552</t>
+          <t>142589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194636</t>
+          <t>195380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>337568</t>
+          <t>336773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>643041</t>
+          <t>659247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>490442</t>
+          <t>484184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>969026</t>
+          <t>937984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>429643</t>
+          <t>428899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482727</t>
+          <t>481690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206224</t>
+          <t>190018</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>511697</t>
+          <t>512492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>504518</t>
+          <t>535560</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>983102</t>
+          <t>989360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41313</t>
+          <t>46720</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>136839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202032</t>
+          <t>202028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>244463</t>
+          <t>244886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>199850</t>
+          <t>190024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>382436</t>
+          <t>382352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>792765</t>
+          <t>791881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>887407</t>
+          <t>882000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>470388</t>
+          <t>469965</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>512819</t>
+          <t>512823</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1261136</t>
+          <t>1261220</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1443722</t>
+          <t>1453548</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>602104</t>
+          <t>606557</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>855818</t>
+          <t>862316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1387080</t>
+          <t>1376601</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1944977</t>
+          <t>1886597</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2074461</t>
+          <t>2089193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2778298</t>
+          <t>2761143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2603999</t>
+          <t>2597501</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2857713</t>
+          <t>2853260</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1713621</t>
+          <t>1772001</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2271518</t>
+          <t>2281997</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4340117</t>
+          <t>4357272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5043954</t>
+          <t>5029222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51906</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>61249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>69015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102532</t>
+          <t>102406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221104</t>
+          <t>222098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245163</t>
+          <t>246103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198967</t>
+          <t>199589</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224278</t>
+          <t>224781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431316</t>
+          <t>431442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>463730</t>
+          <t>464833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34206</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>62487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95327</t>
+          <t>96583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130379</t>
+          <t>130753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137789</t>
+          <t>137067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182319</t>
+          <t>181959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432477</t>
+          <t>430588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458869</t>
+          <t>457952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>373196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>408622</t>
+          <t>407366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>814705</t>
+          <t>815065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859235</t>
+          <t>859957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>47257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80564</t>
+          <t>80629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113369</t>
+          <t>114248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112602</t>
+          <t>110308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153029</t>
+          <t>151751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270034</t>
+          <t>271589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293562</t>
+          <t>293807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222043</t>
+          <t>221164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254848</t>
+          <t>254783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501229</t>
+          <t>502507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541656</t>
+          <t>543950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68219</t>
+          <t>66624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68142</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100881</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116694</t>
+          <t>117352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159498</t>
+          <t>158616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290452</t>
+          <t>292047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316156</t>
+          <t>318192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270575</t>
+          <t>271476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303314</t>
+          <t>302083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>570629</t>
+          <t>571511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613433</t>
+          <t>612775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65439</t>
+          <t>66943</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65446</t>
+          <t>65944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98752</t>
+          <t>98332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163267</t>
+          <t>163597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183110</t>
+          <t>182805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142229</t>
+          <t>140725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>167451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312224</t>
+          <t>312644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345530</t>
+          <t>345032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48147</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>55141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82758</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87080</t>
+          <t>87593</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123815</t>
+          <t>124244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222664</t>
+          <t>221754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244268</t>
+          <t>244366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195386</t>
+          <t>194900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222411</t>
+          <t>223003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425140</t>
+          <t>424711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461875</t>
+          <t>461362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69097</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103771</t>
+          <t>104961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112440</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156425</t>
+          <t>156012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194216</t>
+          <t>193405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248456</t>
+          <t>249405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511256</t>
+          <t>510066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545930</t>
+          <t>544612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>481794</t>
+          <t>482207</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>525779</t>
+          <t>526024</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1004790</t>
+          <t>1003841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1059030</t>
+          <t>1059841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110165</t>
+          <t>113122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151505</t>
+          <t>152006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188930</t>
+          <t>186877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238819</t>
+          <t>238570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>312675</t>
+          <t>313216</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>378531</t>
+          <t>378149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>590771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>632612</t>
+          <t>629655</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>544692</t>
+          <t>544941</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>594581</t>
+          <t>596634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147757</t>
+          <t>1148139</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1213613</t>
+          <t>1213072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>494030</t>
+          <t>496828</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>758119</t>
+          <t>752583</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>857376</t>
+          <t>853098</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1197256</t>
+          <t>1194525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1327501</t>
+          <t>1326086</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2781495</t>
+          <t>2778697</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2855737</t>
+          <t>2856729</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2521821</t>
+          <t>2526099</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2621078</t>
+          <t>2626614</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5327221</t>
+          <t>5328636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5457466</t>
+          <t>5460197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>63570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58964</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89554</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103136</t>
+          <t>104246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145189</t>
+          <t>145417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228464</t>
+          <t>228625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255327</t>
+          <t>255751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194428</t>
+          <t>193987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225018</t>
+          <t>224517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>430987</t>
+          <t>430759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473040</t>
+          <t>471930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89183</t>
+          <t>88569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126068</t>
+          <t>126051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160619</t>
+          <t>158180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203813</t>
+          <t>204584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257106</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317915</t>
+          <t>319147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416344</t>
+          <t>416958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318918</t>
+          <t>318147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362112</t>
+          <t>364551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710343</t>
+          <t>709111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771152</t>
+          <t>768905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88334</t>
+          <t>87489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92127</t>
+          <t>93916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128570</t>
+          <t>129368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157886</t>
+          <t>159592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206079</t>
+          <t>205679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234782</t>
+          <t>235627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264981</t>
+          <t>266808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212450</t>
+          <t>211652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248893</t>
+          <t>247104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>458457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>506250</t>
+          <t>504544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91562</t>
+          <t>91979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138668</t>
+          <t>139209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176540</t>
+          <t>176733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207075</t>
+          <t>202409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258288</t>
+          <t>257627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282420</t>
+          <t>282003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316389</t>
+          <t>316668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211434</t>
+          <t>211241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249306</t>
+          <t>248765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503668</t>
+          <t>504329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554881</t>
+          <t>559547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>48806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83260</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113733</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114083</t>
+          <t>114534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155183</t>
+          <t>154971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164611</t>
+          <t>163812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186801</t>
+          <t>186693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105858</t>
+          <t>105981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136331</t>
+          <t>136736</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277026</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318126</t>
+          <t>317675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>68398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88937</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122950</t>
+          <t>121947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139312</t>
+          <t>137833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180351</t>
+          <t>183453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207434</t>
+          <t>205583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233243</t>
+          <t>232789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156190</t>
+          <t>157193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190203</t>
+          <t>190915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372770</t>
+          <t>369668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413809</t>
+          <t>415288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93126</t>
+          <t>92828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137042</t>
+          <t>133847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199740</t>
+          <t>199041</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249451</t>
+          <t>249419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304721</t>
+          <t>303729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>371436</t>
+          <t>368765</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>525746</t>
+          <t>528941</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569662</t>
+          <t>569960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>444402</t>
+          <t>444434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>494113</t>
+          <t>494812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>985205</t>
+          <t>987876</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1051920</t>
+          <t>1052912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91910</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132566</t>
+          <t>132256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213168</t>
+          <t>212738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266891</t>
+          <t>266932</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>317768</t>
+          <t>317050</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>386917</t>
+          <t>387149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644406</t>
+          <t>644716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>685062</t>
+          <t>685345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>555812</t>
+          <t>555771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>609535</t>
+          <t>609965</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1212758</t>
+          <t>1212526</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1281907</t>
+          <t>1282625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>564915</t>
+          <t>561679</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>663418</t>
+          <t>661042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1134909</t>
+          <t>1129220</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1247662</t>
+          <t>1246793</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1729485</t>
+          <t>1725197</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1884212</t>
+          <t>1880104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2757761</t>
+          <t>2760137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2856264</t>
+          <t>2859500</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2303333</t>
+          <t>2304202</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2416086</t>
+          <t>2421775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5087962</t>
+          <t>5092070</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5242689</t>
+          <t>5246977</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49110</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78087</t>
+          <t>78659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81202</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114513</t>
+          <t>112974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136679</t>
+          <t>137801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182161</t>
+          <t>183206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215674</t>
+          <t>215102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>243661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>175729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207501</t>
+          <t>208622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>400303</t>
+          <t>399258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>445785</t>
+          <t>444663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>70764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104076</t>
+          <t>105010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>137549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178078</t>
+          <t>180284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215081</t>
+          <t>212616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>270119</t>
+          <t>271216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398499</t>
+          <t>397565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431552</t>
+          <t>431811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345006</t>
+          <t>342800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>386900</t>
+          <t>385535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>755540</t>
+          <t>754443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810578</t>
+          <t>813043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50585</t>
+          <t>49574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93686</t>
+          <t>93955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129519</t>
+          <t>129772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152535</t>
+          <t>152600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195234</t>
+          <t>195955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242540</t>
+          <t>242789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267980</t>
+          <t>268991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206790</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242623</t>
+          <t>242354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459640</t>
+          <t>458919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>502339</t>
+          <t>502274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88552</t>
+          <t>88290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123449</t>
+          <t>123234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157214</t>
+          <t>157216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>196745</t>
+          <t>198427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255559</t>
+          <t>256605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308568</t>
+          <t>311558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246515</t>
+          <t>246730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>281412</t>
+          <t>281674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190538</t>
+          <t>188856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230069</t>
+          <t>230067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448679</t>
+          <t>445689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>501688</t>
+          <t>500642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52862</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78563</t>
+          <t>78998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79701</t>
+          <t>77499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113522</t>
+          <t>111086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169598</t>
+          <t>171903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190819</t>
+          <t>191374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140024</t>
+          <t>139589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165725</t>
+          <t>166831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316286</t>
+          <t>318722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350107</t>
+          <t>352309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27979</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>55807</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85015</t>
+          <t>84774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130585</t>
+          <t>129923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211517</t>
+          <t>210621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235144</t>
+          <t>233659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188100</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218483</t>
+          <t>217308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405653</t>
+          <t>406315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445998</t>
+          <t>445202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>79391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116342</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132114</t>
+          <t>130881</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176017</t>
+          <t>176408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>222684</t>
+          <t>222037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>283508</t>
+          <t>281028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>540216</t>
+          <t>538551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>575224</t>
+          <t>577167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>515277</t>
+          <t>514886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>559180</t>
+          <t>560413</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1064344</t>
+          <t>1066824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1125168</t>
+          <t>1125815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135273</t>
+          <t>135471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181448</t>
+          <t>181882</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249031</t>
+          <t>247266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>302704</t>
+          <t>304954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>394379</t>
+          <t>392589</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>467581</t>
+          <t>467645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>597135</t>
+          <t>596701</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>643310</t>
+          <t>643112</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>523463</t>
+          <t>521213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577136</t>
+          <t>578901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1137169</t>
+          <t>1137105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1210371</t>
+          <t>1212161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>596489</t>
+          <t>595150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>685443</t>
+          <t>688038</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1045830</t>
+          <t>1050441</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1162104</t>
+          <t>1161428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1673737</t>
+          <t>1673551</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1828832</t>
+          <t>1815264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2708907</t>
+          <t>2706312</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2797861</t>
+          <t>2799200</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2382438</t>
+          <t>2383114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2498712</t>
+          <t>2494101</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5110060</t>
+          <t>5123628</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5265155</t>
+          <t>5265341</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,27 +10697,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>95102</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73330</t>
+          <t>80038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111069</t>
+          <t>113700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>136010</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113308</t>
+          <t>121828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141176</t>
+          <t>149694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>218255</t>
+          <t>231112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196644</t>
+          <t>208463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242434</t>
+          <t>253714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -10810,22 +10810,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>223743</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200374</t>
+          <t>205145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238113</t>
+          <t>238807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>162308</t>
+          <t>180051</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148459</t>
+          <t>166367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176327</t>
+          <t>194233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>382822</t>
+          <t>403794</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358643</t>
+          <t>381192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>404433</t>
+          <t>426443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>119718</t>
+          <t>123088</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99499</t>
+          <t>103620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143140</t>
+          <t>149104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>209328</t>
+          <t>218316</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190479</t>
+          <t>199311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229325</t>
+          <t>239338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>329046</t>
+          <t>341404</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299982</t>
+          <t>311998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>360735</t>
+          <t>378114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>398672</t>
+          <t>407559</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375250</t>
+          <t>381543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418891</t>
+          <t>427027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>304963</t>
+          <t>327493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284966</t>
+          <t>306471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323812</t>
+          <t>346498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>703634</t>
+          <t>735052</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671945</t>
+          <t>698342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732698</t>
+          <t>764458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>92500</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75048</t>
+          <t>77830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108279</t>
+          <t>109690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146969</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131834</t>
+          <t>137222</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162489</t>
+          <t>168382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>237434</t>
+          <t>244717</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215252</t>
+          <t>223067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261360</t>
+          <t>267159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>225586</t>
+          <t>223493</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207771</t>
+          <t>206303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>238163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>202159</t>
+          <t>204165</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186639</t>
+          <t>187999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217294</t>
+          <t>219159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>427744</t>
+          <t>427658</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403818</t>
+          <t>405216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>449926</t>
+          <t>449308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>133147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>166330</t>
+          <t>183414</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>165531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211222</t>
+          <t>203523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>261478</t>
+          <t>293062</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187397</t>
+          <t>264057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303586</t>
+          <t>326018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>217409</t>
+          <t>263498</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195503</t>
+          <t>239998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235360</t>
+          <t>286524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>309388</t>
+          <t>238547</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264496</t>
+          <t>218438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378844</t>
+          <t>256430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>526796</t>
+          <t>502045</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484688</t>
+          <t>469089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>600877</t>
+          <t>531050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50389</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72923</t>
+          <t>75730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91156</t>
+          <t>96430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>123408</t>
+          <t>130282</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110468</t>
+          <t>117831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136381</t>
+          <t>144038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137447</t>
+          <t>161051</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128353</t>
+          <t>151050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146295</t>
+          <t>170770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126543</t>
+          <t>141546</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>130785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135733</t>
+          <t>151485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>263990</t>
+          <t>302597</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251017</t>
+          <t>288841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276930</t>
+          <t>315048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78873</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92916</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98110</t>
+          <t>99989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124023</t>
+          <t>126894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>189408</t>
+          <t>190174</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171117</t>
+          <t>171874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208596</t>
+          <t>207406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>190763</t>
+          <t>193705</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>181152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203200</t>
+          <t>206163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>146521</t>
+          <t>150578</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133033</t>
+          <t>136856</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158946</t>
+          <t>163761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>337284</t>
+          <t>344283</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318096</t>
+          <t>327051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355575</t>
+          <t>362583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,17 +12755,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>166105</t>
+          <t>191537</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142589</t>
+          <t>165781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195380</t>
+          <t>220928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>469240</t>
+          <t>314274</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>336773</t>
+          <t>287539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>659247</t>
+          <t>337458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>635345</t>
+          <t>505812</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484184</t>
+          <t>470137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>937984</t>
+          <t>543088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -12868,17 +12868,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>458174</t>
+          <t>528150</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>428899</t>
+          <t>498759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>481690</t>
+          <t>553906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>380025</t>
+          <t>457783</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190018</t>
+          <t>434599</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>512492</t>
+          <t>484518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>838199</t>
+          <t>985932</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>535560</t>
+          <t>948656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>989360</t>
+          <t>1021607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>94263</t>
+          <t>105836</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46720</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136839</t>
+          <t>127404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>222539</t>
+          <t>251438</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202028</t>
+          <t>228664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>244886</t>
+          <t>274617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>316802</t>
+          <t>357274</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190024</t>
+          <t>327965</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>382352</t>
+          <t>388500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>834457</t>
+          <t>692236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>791881</t>
+          <t>670668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>882000</t>
+          <t>709858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>492312</t>
+          <t>578568</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>469965</t>
+          <t>555389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>512823</t>
+          <t>601342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1326770</t>
+          <t>1270804</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1261220</t>
+          <t>1239578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1453548</t>
+          <t>1300113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>606557</t>
+          <t>786469</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>862316</t>
+          <t>898424</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1376601</t>
+          <t>1401329</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1886597</t>
+          <t>1502432</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2089193</t>
+          <t>2225276</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2761143</t>
+          <t>2370307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2683023</t>
+          <t>2693435</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2597501</t>
+          <t>2634338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2853260</t>
+          <t>2746293</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2124215</t>
+          <t>2278733</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1772001</t>
+          <t>2230809</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2281997</t>
+          <t>2331912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4807238</t>
+          <t>4972167</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4357272</t>
+          <t>4895696</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5029222</t>
+          <t>5040727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
